--- a/data/trans_camb/IP04F-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Estudios-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 1,6</t>
+          <t>-11,29; 2,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 5,59</t>
+          <t>-7,24; 5,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 1,85</t>
+          <t>-7,18; 2,16</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,14; 50,68</t>
+          <t>-87,9; 59,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,83; 271,39</t>
+          <t>-82,9; 222,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,44; 43,9</t>
+          <t>-73,58; 47,15</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,81</t>
+          <t>-3,36; 1,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,77</t>
+          <t>-2,98; 1,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,21</t>
+          <t>-2,37; 1,06</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 35,6</t>
+          <t>-41,54; 30,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 39,15</t>
+          <t>-42,52; 42,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 21,72</t>
+          <t>-33,18; 20,24</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 5,26</t>
+          <t>-9,73; 4,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 2,73</t>
+          <t>-11,59; 2,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 2,01</t>
+          <t>-8,12; 1,56</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 30,76</t>
+          <t>-39,7; 26,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,95; 18,05</t>
+          <t>-46,97; 18,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,31; 11,89</t>
+          <t>-35,55; 8,7</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,06</t>
+          <t>-4,06; 1,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,34</t>
+          <t>-3,65; 1,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,41</t>
+          <t>-2,98; 0,44</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 11,47</t>
+          <t>-34,4; 11,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,3; 16,69</t>
+          <t>-35,1; 16,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 4,46</t>
+          <t>-28,46; 4,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04F-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Estudios-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 2,07</t>
+          <t>-11,98; 1,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 5,33</t>
+          <t>-6,91; 6,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 2,16</t>
+          <t>-7,44; 2,02</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-87,9; 59,02</t>
+          <t>-90,69; 47,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-82,9; 222,04</t>
+          <t>-80,48; 285,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,58; 47,15</t>
+          <t>-73,58; 44,23</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,65</t>
+          <t>-3,49; 1,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,85</t>
+          <t>-3,08; 1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,06</t>
+          <t>-2,47; 0,97</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 30,73</t>
+          <t>-41,49; 37,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,52; 42,06</t>
+          <t>-44,15; 43,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,18; 20,24</t>
+          <t>-34,49; 18,2</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 4,37</t>
+          <t>-9,61; 4,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 2,62</t>
+          <t>-11,35; 2,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 1,56</t>
+          <t>-8,07; 1,27</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,7; 26,11</t>
+          <t>-39,31; 25,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-46,97; 18,76</t>
+          <t>-47,5; 12,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 8,7</t>
+          <t>-36,13; 7,29</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,02</t>
+          <t>-4,24; 1,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,27</t>
+          <t>-3,49; 1,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 0,44</t>
+          <t>-3,03; 0,52</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 11,24</t>
+          <t>-35,13; 11,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 16,2</t>
+          <t>-34,34; 16,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 4,79</t>
+          <t>-29,08; 6,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04F-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Estudios-trans_camb.xlsx
@@ -495,12 +495,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>-5,04</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 1,77</t>
+          <t>-7,19; 5,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 6,47</t>
+          <t>-12,72; 1,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 2,02</t>
+          <t>-7,53; 1,85</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-10,02%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>-52,85%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-10,02%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,69; 47,77</t>
+          <t>-83,83; 271,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,48; 285,1</t>
+          <t>-90,14; 50,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,58; 44,23</t>
+          <t>-74,44; 43,9</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,66</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>-0,77</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,84</t>
+          <t>-3,01; 1,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,87</t>
+          <t>-3,42; 1,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,97</t>
+          <t>-2,49; 1,21</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-11,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>-11,4%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-11,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 37,22</t>
+          <t>-44,88; 39,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,15; 43,67</t>
+          <t>-41,15; 35,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 18,2</t>
+          <t>-35,65; 21,72</t>
         </is>
       </c>
     </row>
@@ -740,12 +740,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>-2,29</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-4,16</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 4,12</t>
+          <t>-10,55; 2,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 2,04</t>
+          <t>-8,74; 5,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,27</t>
+          <t>-8,36; 2,01</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-20,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>-11,14%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-20,88%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 25,53</t>
+          <t>-45,95; 18,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 12,95</t>
+          <t>-37,18; 30,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 7,29</t>
+          <t>-36,31; 11,89</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>-1,49</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-1,17</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,01</t>
+          <t>-3,26; 1,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,25</t>
+          <t>-4,02; 1,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,52</t>
+          <t>-3,05; 0,41</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-13,05%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>-14,31%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-13,05%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 11,42</t>
+          <t>-33,3; 16,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 16,18</t>
+          <t>-34,82; 11,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 6,04</t>
+          <t>-28,8; 4,46</t>
         </is>
       </c>
     </row>
